--- a/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
+++ b/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
@@ -1312,14 +1312,14 @@
       <c r="B12" s="80" t="inlineStr">
         <is>
           <t>Isporuka i montaža nosive metalne konstrukcije (ground mount support) za prihvat fotonaponskih panela, karakteristika:
- - tip: A-izvedba, NISKA izvedba (Standard A-Shaped Support 3.0 — LOW SUPPORT), kao Huawei BOM 21540481 sa ankerima BOM 21540482, antitheft maticom 21540036 i ključem 21540038, ili ekvivalent istih ili boljih karakteristika
+ - tip: CUSTOM IZRADA (izvan kataloga zbog opterećenja vjetrom, v. niže) — 3 nosača, svaki za 4 fotonaponska modula (2 reda × 2 kolone, portret); geometrija margina/prepusta preuzeta iz Huawei Standard A-Shaped Support 3.0 konvencije (PVM Tabela 4-20), ali poprečna greda izrađena po mjeri za 2 kolone modula, ne za kataloških 6
  - inklinacija: fiksno 45°, orijentacija JUG (azimut 180°). Nagib je zadržan zbog decembarskog prinosa — pri podnevnoj visini Sunca 23,6° na 42,94° N nagib 45° ostvaruje 93 % direktnog zračenja u odnosu na 85 % pri 35°, a decembar je mjerodavni mjesec za dimenzionisanje autonomnog sistema
- - gabariti PV polja (2 reda × 3 modula, portret): širina polja 3476 mm (poprečna greda 4089 mm, bočni prepust 306,5 mm), dužina polja po nagibu 4576 mm (2 × 2278 mm), horizontalna projekcija 3236 mm pri nagibu 45°; donja ivica panela na +0,50 m, gornja ivica na +3,74 m od nivoa terena
- - smještaj: nosač se temelji IZVAN ograđenog platoa, 1400 mm južno od kote ograde (raspoloživi pojas 1950 mm); gornja (sjeverna) ivica panela je 1,84 m iznad kote ograde h=1,90 m i prelazi preko platoa na visini +3,50 m, iznad krova kontejnera. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
- - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥27 kN, horizontalna sila ≥30 kN, moment prevrtanja ≥64 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh)
+ - gabariti PV polja po nosaču (2 reda × 2 modula, portret): širina polja 2305 mm (poprečna greda 2918 mm, bočni prepust 306,5 mm), dužina polja po nagibu 4576 mm (2 × 2278 mm, nepromijenjeno), horizontalna projekcija 3236 mm pri nagibu 45°; donja ivica panela na +1,50 m, gornja ivica na +4,74 m od nivoa terena — podignuto za 1,00 m u odnosu na raniju 2×6 izvedbu, jer manje opterećenje vjetra po nosaču to dopušta (v. proračun F.6)
+ - smještaj: nosači se temelje IZVAN ograđenog platoa, 400 mm južno od kote ograde (raspoloživi pojas 1950 mm); gornja (sjeverna) ivica panela je 2,84 m iznad kote ograde h=1,90 m. Ponuđač provjerava da konstrukcija u cijelosti ostaje unutar zakupljene parcele 16,00 × 9,40 m
+ - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 10,55 m² po nosaču (2305 × 4576 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥18,1 kN, horizontalna sila ≥13,4 kN, moment prevrtanja ≥62,8 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
  - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
  - spojni pribor: nehrđajući čelik A2/A4
- - uključeno ožičenje i povezivanje oba polja panela do PVDB distribucije</t>
+ - uključeno ožičenje i povezivanje sva tri polja panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. Tačku 1.6a i crtež E-01): PV-1 i PV-2 paralelno na rutu 1, PV-3 samostalno na rutu 2</t>
         </is>
       </c>
       <c r="C12" s="79" t="inlineStr">
@@ -1328,7 +1328,7 @@
         </is>
       </c>
       <c r="D12" s="79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" s="27" t="n"/>
       <c r="F12" s="27">
@@ -1475,9 +1475,9 @@
           <t>Isporuka i ugradnja sistema sidrenja nosive konstrukcije iz Tačke 1.1 u stijenu/beton, hemijskim (epoksidnim) ankerima.
  - tip: hemijski (epoksidni/vinilesterski) anker M16 ili M20 sa ETA odobrenjem za ugradnju u beton i/ili stijenu, vruće cinčan ili nehrđajući A4
  - broj: najmanje 2 ankera po temeljnoj traci, odnosno 4 ankera po nosaču (minimum 2 po traci zbog redundanse)
- - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥27 kN (GSN)
+ - nosivost: karakteristična sila čupanja ≥30 kN po ankeru; dubina ugradnje prema ETA za konkretnu podlogu. Ukupna projektna sila podizanja po nosaču ≥18,1 kN (GSN); sila po traci od momenta prevrtanja ≥39,3 kN pri razmaku traka 1600 mm (v. proračun F.6)
  - dokazivanje: ispitivanje čupanjem (pull-out test) na najmanje 10 % ugrađenih ankera, minimalno 2 po nosaču, do 1,5 × projektne sile, uz zapisnik ovjeren od nadzornog organa
- - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj zapremine ≥1,14 m³ po nosaču (umjesto 0,81 m³)</t>
+ - alternativa: livena U-anker sidra M16, dužine 320 mm, razmaka krakova 180 mm, sa pločama 50×50 mm i dvostrukim maticama, dozvoljena su SAMO uz gravitacioni temelj zapremine ≥0,75 m³ po nosaču (tendovano 0,81 m³ po nosaču, v. Tačku 2.3) — momenat prevrtanja i dalje zahtijeva provjeru lokalnog istezanja trake, ne samo ukupne mase</t>
         </is>
       </c>
       <c r="C29" s="79" t="inlineStr">
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="D29" s="79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" s="27" t="n"/>
       <c r="F29" s="27">
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="D33" s="89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E33" s="41" t="n"/>
       <c r="F33" s="41">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B34" s="91" t="inlineStr">
         <is>
-          <t>Isporuka i polaganje DC solarnog kabla 1×6 mm² (H1Z2Z2-K) od fotonaponskih panela do PVDB distribucije, uključujući MC4 konektore, obujmice i UV-otporne kanalice. NAPOMENA: završni priključak na ulaznu stezaljku iSSU modula izvesti presjekom 4 mm² prema izričitom zahtjevu proizvođača. Pad napona pri Imp 13,67 A i dužini 25 m iznosi 0,78 %. 2 nosača × 2 × 25,00 m</t>
+          <t>Isporuka i polaganje DC solarnog kabla 1×6 mm² (H1Z2Z2-K) od fotonaponskih panela do PVDB distribucije, uključujući MC4 konektore, obujmice i UV-otporne kanalice. NAPOMENA: završni priključak na ulaznu stezaljku iSSU modula izvesti presjekom 4 mm² prema izričitom zahtjevu proizvođača. Pad napona pri Imp 13,67 A i dužini 25 m iznosi 0,78 %. 3 nosača × 2 × 25,00 m</t>
         </is>
       </c>
       <c r="C34" s="89" t="inlineStr">
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D34" s="89" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E34" s="41" t="n"/>
       <c r="F34" s="41">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B36" s="91" t="inlineStr">
         <is>
-          <t>Isporuka i ugradnja odvodnika prenapona DC, tip 2 (Iimp ≥5 kA, Ucpv ≥425 V), za svaki string, sa pripadajućim rastavnim osiguračima, u PVDB ormaru iz Tačke 1.6 ili u zasebnom kućištu min. IP55. Predvidjeti drugi komplet na strani polja panela zbog dužine DC trase od 25 m.</t>
+          <t>Isporuka i ugradnja odvodnika prenapona DC, tip 2 (Iimp ≥5 kA, Ucpv ≥425 V), za svaki string, sa pripadajućim rastavnim osiguračima, u PVDB ormaru iz Tačke 1.6 ili u zasebnom kućištu min. IP55. Po jedan komplet uz svako od tri polja panela (v. Tačku 1.1) zbog dužine DC trase od 25 m; PV-1 i PV-2 se spajaju paralelno prije PVDB rute 1, PV-3 ide samostalno na rutu 2 (v. crtež E-01).</t>
         </is>
       </c>
       <c r="C36" s="89" t="inlineStr">
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="D36" s="89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" s="41" t="n"/>
       <c r="F36" s="41">
@@ -1665,68 +1665,70 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="B38" s="90" t="inlineStr">
-        <is>
-          <t>OPCIJA (alternativna ponuda — cijena se iskazuje posebno i NE ulazi u zbir Tačke 1): Isporuka i montaža TRI nosača sa po 4 fotonaponska modula (3 × 4 = 12 modula, ista ukupna snaga 7,02 kWp) umjesto dva nosača sa po 6 modula. Površina izloženosti vjetru po nosaču smanjuje se sa 15,91 m² na 7,95 m² (−50 %), čime se približno prepolovljuju sila podizanja i moment prevrtanja po temelju, uz zadržavanje nagiba 45°. Uključuje treći komplet temelja, sidrenja i uzemljenja. Kupac zadržava pravo izbora između osnovne i alternativne izvedbe.</t>
-        </is>
-      </c>
-      <c r="C38" s="89" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="D38" s="89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="41" t="n"/>
-      <c r="F38" s="41" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="92" t="inlineStr">
+      <c r="A38" s="92" t="inlineStr">
         <is>
           <t>UKUPNO 1 — NOSAČI ZA FOTONAPONSKE PANELE:</t>
         </is>
       </c>
-      <c r="B39" s="93" t="n"/>
-      <c r="C39" s="93" t="n"/>
-      <c r="D39" s="93" t="n"/>
-      <c r="E39" s="94" t="n"/>
-      <c r="F39" s="67">
-        <f>SUM(F12:F38)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" s="69"/>
+      <c r="B38" s="93" t="n"/>
+      <c r="C38" s="93" t="n"/>
+      <c r="D38" s="93" t="n"/>
+      <c r="E38" s="94" t="n"/>
+      <c r="F38" s="67">
+        <f>SUM(F12:F37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" s="69">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>GRAĐEVINSKI RADOVI</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+    </row>
     <row r="41" ht="24" customHeight="1" s="69">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>GRAĐEVINSKI RADOVI</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n"/>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B41" s="77" t="inlineStr">
+        <is>
+          <t>Iskop zemlje IV-V kategorije za temeljne trake nosača. Iskop cca 1,59 m3 za svaku temeljnu traku. 3 nosača × 2 trake × 1,59 m3</t>
+        </is>
+      </c>
+      <c r="C41" s="76" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="D41" s="76" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="E41" s="8" t="n"/>
+      <c r="F41" s="8">
+        <f>IF(AND(D41&lt;&gt;"",E41&lt;&gt;""),D41*E41,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2.1</t>
-        </is>
-      </c>
-      <c r="B42" s="77" t="inlineStr">
-        <is>
-          <t>Iskop zemlje IV-V kategorije za temeljne trake nosača. Iskop cca 1,59 m3 za svaku temeljnu traku. 2 nosača × 2 trake × 1,59 m3</t>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B42" s="78" t="inlineStr">
+        <is>
+          <t>Zatrpavanje rova zemljom od iskopa uz nabijanje u slojevima. 3 nosača × 2 trake × 1,10 m3</t>
         </is>
       </c>
       <c r="C42" s="76" t="inlineStr">
@@ -1735,7 +1737,7 @@
         </is>
       </c>
       <c r="D42" s="76" t="n">
-        <v>6.36</v>
+        <v>6.6</v>
       </c>
       <c r="E42" s="8" t="n"/>
       <c r="F42" s="8">
@@ -1746,12 +1748,12 @@
     <row r="43" ht="24" customHeight="1" s="69">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2.2</t>
-        </is>
-      </c>
-      <c r="B43" s="78" t="inlineStr">
-        <is>
-          <t>Zatrpavanje rova zemljom od iskopa uz nabijanje u slojevima. 2 nosača × 2 trake × 1,10 m3</t>
+          <t>2.2a</t>
+        </is>
+      </c>
+      <c r="B43" s="77" t="inlineStr">
+        <is>
+          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km.</t>
         </is>
       </c>
       <c r="C43" s="76" t="inlineStr">
@@ -1760,7 +1762,7 @@
         </is>
       </c>
       <c r="D43" s="76" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="E43" s="8" t="n"/>
       <c r="F43" s="8">
@@ -1771,12 +1773,12 @@
     <row r="44" ht="156" customHeight="1" s="69">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2.2a</t>
+          <t>2.2b</t>
         </is>
       </c>
       <c r="B44" s="77" t="inlineStr">
         <is>
-          <t>Odvoz i zbrinjavanje viška materijala od iskopa do deponije udaljene do 20 km.</t>
+          <t>Nabavka materijala, transport i ugradnja betona C10 ispod temeljnih traka, prema zahtjevima proizvođača. 3 nosača × 2 trake × 0,094 m3</t>
         </is>
       </c>
       <c r="C44" s="76" t="inlineStr">
@@ -1785,7 +1787,7 @@
         </is>
       </c>
       <c r="D44" s="76" t="n">
-        <v>1.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E44" s="8" t="n"/>
       <c r="F44" s="8">
@@ -1796,12 +1798,13 @@
     <row r="45" ht="24" customHeight="1" s="69">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2.2b</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="B45" s="77" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i ugradnja betona C10 ispod temeljnih traka, prema zahtjevima proizvođača. 2 nosača × 2 trake × 0,094 m3</t>
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C25, uz upotrebu oplate za nadzemni dio. Traka je širine 450 mm (550 mm u dnu), dužine 3300 mm i dubine 900 mm, postavljena u pravcu SJEVER-JUG (u pravcu nagiba panela), na osovinskom razmaku 1600 mm, sve prema nacrtu proizvođača nosača. Armiranje rebrastom armaturom Ø10, granica razvlačenja 335 MPa, prema specifikaciji proizvođača (poz. R01–R04, cca 19,53 kg po traci, ukupno cca 78 kg), zaštitni sloj betona 50 mm — što ulazi u cijenu betona. Prije betoniranja pravilno pozicionirati anker vijke iz Tačke 1.2 (vezani za armaturu poz. R04), uzemljivačku traku i PEHD cijevi. Ugradnja betona pervibratorom, njega betona vlaženjem najmanje 3 dana, dozvoljeno odstupanje ±3 mm. NAPOMENA: nosivost tla ispod temelja (fak) mora iznositi najmanje 100 kPa, a osnovna brzina vjetra za nagib 45° iznosi 31 m/s (3 s udar). Proizvođač izričito zahtijeva da se za lokacije na planinskim vrhovima projekat temelja ponovo provjeri i prilagodi. 3 nosača × 2 trake × 0,407 m3.  Obračun po ostvarenom m3 betona.
+IZMJENA — BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina trake prema ovjerenom statičkom proračunu iz Tačke 1.3.</t>
         </is>
       </c>
       <c r="C45" s="76" t="inlineStr">
@@ -1810,7 +1813,7 @@
         </is>
       </c>
       <c r="D45" s="76" t="n">
-        <v>0.38</v>
+        <v>2.44</v>
       </c>
       <c r="E45" s="8" t="n"/>
       <c r="F45" s="8">
@@ -1821,24 +1824,22 @@
     <row r="46" s="69">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="B46" s="77" t="inlineStr">
-        <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C25, uz upotrebu oplate za nadzemni dio. Traka je širine 450 mm (550 mm u dnu), dužine 3300 mm i dubine 900 mm, postavljena u pravcu SJEVER-JUG (u pravcu nagiba panela), na osovinskom razmaku 2600 mm, sve prema nacrtu proizvođača nosača. Armiranje rebrastom armaturom Ø10, granica razvlačenja 335 MPa, prema specifikaciji proizvođača (poz. R01–R04, cca 19,53 kg po traci, ukupno cca 78 kg), zaštitni sloj betona 50 mm — što ulazi u cijenu betona. Prije betoniranja pravilno pozicionirati anker vijke iz Tačke 1.2 (vezani za armaturu poz. R04), uzemljivačku traku i PEHD cijevi. Ugradnja betona pervibratorom, njega betona vlaženjem najmanje 3 dana, dozvoljeno odstupanje ±3 mm. NAPOMENA: nosivost tla ispod temelja (fak) mora iznositi najmanje 100 kPa, a osnovna brzina vjetra za nagib 45° iznosi 31 m/s (3 s udar). Proizvođač izričito zahtijeva da se za lokacije na planinskim vrhovima projekat temelja ponovo provjeri i prilagodi. 2 nosača × 2 trake × 0,407 m3.  Obračun po ostvarenom m3 betona.
-IZMJENA — BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina trake prema ovjerenom statičkom proračunu iz Tačke 1.3.</t>
-        </is>
-      </c>
-      <c r="C46" s="76" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="D46" s="76" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E46" s="8" t="n"/>
+          <t>2.4</t>
+        </is>
+      </c>
+      <c r="B46" s="97" t="inlineStr">
+        <is>
+          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>12</v>
+      </c>
       <c r="F46" s="8">
         <f>IF(AND(D46&lt;&gt;"",E46&lt;&gt;""),D46*E46,"")</f>
         <v/>
@@ -1847,125 +1848,118 @@
     <row r="47" s="69">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2.4</t>
-        </is>
-      </c>
-      <c r="B47" s="97" t="inlineStr">
-        <is>
-          <t>Obrada vidljivih strana i gornje površine temeljnih traka cementnim malterom u nagibu 1,0 %, zaglađeno do crnog sjaja.</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>m2</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>12</v>
-      </c>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="B47" s="78" t="inlineStr">
+        <is>
+          <t>Ostali sitni građevinski i potrošni materijal.</t>
+        </is>
+      </c>
+      <c r="C47" s="76" t="inlineStr">
+        <is>
+          <t>paušal</t>
+        </is>
+      </c>
+      <c r="D47" s="76" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="8" t="n"/>
       <c r="F47" s="8">
         <f>IF(AND(D47&lt;&gt;"",E47&lt;&gt;""),D47*E47,"")</f>
         <v/>
       </c>
     </row>
     <row r="48" s="69">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="B48" s="78" t="inlineStr">
-        <is>
-          <t>Ostali sitni građevinski i potrošni materijal.</t>
-        </is>
-      </c>
-      <c r="C48" s="76" t="inlineStr">
-        <is>
-          <t>paušal</t>
-        </is>
-      </c>
-      <c r="D48" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8">
-        <f>IF(AND(D48&lt;&gt;"",E48&lt;&gt;""),D48*E48,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" s="69">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>UKUPNO 2 — GRAĐEVINSKI RADOVI ZA NOSAČE FN PANELA:</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="10">
-        <f>SUM(F42:F48)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="95" t="inlineStr">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="10">
+        <f>SUM(F41:F47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" s="69"/>
+    <row r="50">
+      <c r="A50" s="95" t="inlineStr">
         <is>
           <t>UKUPNO LOT 1 — NOSAČI ZA FOTONAPONSKE PANELE (bez PDV-a):</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="11">
-        <f>F39+F49</f>
-        <v/>
-      </c>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="11">
+        <f>F38+F48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="98" t="inlineStr">
+        <is>
+          <t>REKAPITULACIJA — LOT 1</t>
+        </is>
+      </c>
+      <c r="B52" s="103" t="n"/>
+      <c r="C52" s="103" t="n"/>
+      <c r="D52" s="103" t="n"/>
+      <c r="E52" s="104" t="n"/>
+      <c r="F52" s="100" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="98" t="inlineStr">
-        <is>
-          <t>REKAPITULACIJA — LOT 1</t>
+      <c r="A53" s="101" t="inlineStr">
+        <is>
+          <t>UKUPNO LOT 1 (bez PDV-a):</t>
         </is>
       </c>
       <c r="B53" s="103" t="n"/>
       <c r="C53" s="103" t="n"/>
       <c r="D53" s="103" t="n"/>
       <c r="E53" s="104" t="n"/>
-      <c r="F53" s="100" t="n"/>
+      <c r="F53" s="102">
+        <f>F50</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="101" t="inlineStr">
         <is>
-          <t>UKUPNO LOT 1 (bez PDV-a):</t>
+          <t>Popust (%):</t>
         </is>
       </c>
       <c r="B54" s="103" t="n"/>
       <c r="C54" s="103" t="n"/>
       <c r="D54" s="103" t="n"/>
       <c r="E54" s="104" t="n"/>
-      <c r="F54" s="102">
-        <f>F51</f>
-        <v/>
-      </c>
+      <c r="F54" s="102" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="101" t="inlineStr">
         <is>
-          <t>Popust (%):</t>
+          <t>UKUPNO LOT 1 sa popustom (bez PDV-a):</t>
         </is>
       </c>
       <c r="B55" s="103" t="n"/>
       <c r="C55" s="103" t="n"/>
       <c r="D55" s="103" t="n"/>
       <c r="E55" s="104" t="n"/>
-      <c r="F55" s="102" t="n"/>
+      <c r="F55" s="102">
+        <f>F53*(1-IF(F54="",0,F54/100))</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="101" t="inlineStr">
         <is>
-          <t>UKUPNO LOT 1 sa popustom (bez PDV-a):</t>
+          <t>PDV 17%:</t>
         </is>
       </c>
       <c r="B56" s="103" t="n"/>
@@ -1973,40 +1967,26 @@
       <c r="D56" s="103" t="n"/>
       <c r="E56" s="104" t="n"/>
       <c r="F56" s="102">
-        <f>F54*(1-IF(F55="",0,F55/100))</f>
+        <f>F55*0.17</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" s="69">
-      <c r="A57" s="101" t="inlineStr">
-        <is>
-          <t>PDV 17%:</t>
+      <c r="A57" s="98" t="inlineStr">
+        <is>
+          <t>UKUPNO LOT 1 sa PDV-om:</t>
         </is>
       </c>
       <c r="B57" s="103" t="n"/>
       <c r="C57" s="103" t="n"/>
       <c r="D57" s="103" t="n"/>
       <c r="E57" s="104" t="n"/>
-      <c r="F57" s="102">
-        <f>F56*0.17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="98" t="inlineStr">
-        <is>
-          <t>UKUPNO LOT 1 sa PDV-om:</t>
-        </is>
-      </c>
-      <c r="B58" s="103" t="n"/>
-      <c r="C58" s="103" t="n"/>
-      <c r="D58" s="103" t="n"/>
-      <c r="E58" s="104" t="n"/>
-      <c r="F58" s="100">
-        <f>F56+F57</f>
-        <v/>
-      </c>
-    </row>
+      <c r="F57" s="100">
+        <f>F55+F56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58"/>
     <row r="59" ht="24" customHeight="1" s="69"/>
     <row r="83" ht="24" customHeight="1" s="69"/>
     <row r="84" ht="24" customHeight="1" s="69"/>
@@ -4104,7 +4084,7 @@
       <c r="D132" s="9" t="n"/>
       <c r="E132" s="9" t="n"/>
       <c r="F132" s="8">
-        <f>'LOT 1'!F51</f>
+        <f>'LOT 1'!F50</f>
         <v/>
       </c>
     </row>

--- a/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
+++ b/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
@@ -1197,6 +1197,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="70" t="inlineStr">
         <is>
@@ -1211,6 +1212,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
@@ -1679,6 +1681,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40" ht="24" customHeight="1" s="69">
       <c r="A40" s="3" t="inlineStr">
         <is>
@@ -1778,7 +1781,7 @@
       </c>
       <c r="B44" s="77" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i ugradnja betona C10 ispod temeljnih traka, prema zahtjevima proizvođača. 3 nosača × 2 trake × 0,094 m3</t>
+          <t>Nabavka materijala, transport i ugradnja podložnog betona C12/15 ispod temeljnih traka, prema zahtjevima proizvođača. 3 nosača × 2 trake × 0,094 m3</t>
         </is>
       </c>
       <c r="C44" s="76" t="inlineStr">
@@ -1803,7 +1806,7 @@
       </c>
       <c r="B45" s="77" t="inlineStr">
         <is>
-          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C25, uz upotrebu oplate za nadzemni dio. Traka je širine 450 mm (550 mm u dnu), dužine 3300 mm i dubine 900 mm, postavljena u pravcu SJEVER-JUG (u pravcu nagiba panela), na osovinskom razmaku 1600 mm, sve prema nacrtu proizvođača nosača. Armiranje rebrastom armaturom Ø10, granica razvlačenja 335 MPa, prema specifikaciji proizvođača (poz. R01–R04, cca 19,53 kg po traci, ukupno cca 78 kg), zaštitni sloj betona 50 mm — što ulazi u cijenu betona. Prije betoniranja pravilno pozicionirati anker vijke iz Tačke 1.2 (vezani za armaturu poz. R04), uzemljivačku traku i PEHD cijevi. Ugradnja betona pervibratorom, njega betona vlaženjem najmanje 3 dana, dozvoljeno odstupanje ±3 mm. NAPOMENA: nosivost tla ispod temelja (fak) mora iznositi najmanje 100 kPa, a osnovna brzina vjetra za nagib 45° iznosi 31 m/s (3 s udar). Proizvođač izričito zahtijeva da se za lokacije na planinskim vrhovima projekat temelja ponovo provjeri i prilagodi. 3 nosača × 2 trake × 0,407 m3.  Obračun po ostvarenom m3 betona.
+          <t>Nabavka materijala, transport i betoniranje DVIJE temeljne trake po nosaču, betonom C30/37 klase izloženosti XC4 + XF3 prema BAS EN 206 (aerant 4–6 %, Dmax 16, konzistencija S3), uz upotrebu oplate i njegovanje betona. Armatura B500B, zaštitni sloj ≥50 mm, prema ovjerenom statičkom proračunu iz Tačke 1.3. Obračun po m³ ugrađenog betona. 3 nosača × 2 trake × 0,41 m³
 IZMJENA — BETON I ARMATURA: beton klase C30/37, klase izloženosti XC4 + XF3 prema BAS EN 206, sa aerantom 4–6 %, Dmax 16, konzistencija S3; podložni beton C12/15 d=50 mm; armatura B500B, zaštitni sloj ≥50 mm. Klasa XF3 je mjerodavna zbog cikličnog smrzavanja i odmrzavanja u vlažnom stanju na 1076 m n.v. Temeljna spojnica mora biti ispod dubine smrzavanja za lokalitet, koju Ponuđač navodi u ponudi. Dubina trake prema ovjerenom statičkom proračunu iz Tačke 1.3.</t>
         </is>
       </c>
@@ -1988,20 +1991,63 @@
     </row>
     <row r="58"/>
     <row r="59" ht="24" customHeight="1" s="69"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72"/>
+    <row r="73"/>
+    <row r="74"/>
+    <row r="75"/>
+    <row r="76"/>
+    <row r="77"/>
+    <row r="78"/>
+    <row r="79"/>
+    <row r="80"/>
+    <row r="81"/>
+    <row r="82"/>
     <row r="83" ht="24" customHeight="1" s="69"/>
     <row r="84" ht="24" customHeight="1" s="69"/>
+    <row r="85"/>
     <row r="86" ht="24" customHeight="1" s="69"/>
+    <row r="87"/>
+    <row r="88"/>
+    <row r="89"/>
     <row r="90" ht="24" customHeight="1" s="69"/>
     <row r="91" ht="36" customHeight="1" s="69"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
     <row r="98"/>
+    <row r="99"/>
+    <row r="100"/>
     <row r="101" ht="24" customHeight="1" s="69"/>
     <row r="102" ht="24" customHeight="1" s="69"/>
     <row r="103" ht="24" customHeight="1" s="69"/>
+    <row r="104"/>
+    <row r="105"/>
+    <row r="106"/>
     <row r="107" ht="24" customHeight="1" s="69"/>
     <row r="108" ht="24" customHeight="1" s="69"/>
+    <row r="109"/>
     <row r="110" ht="24" customHeight="1" s="69"/>
+    <row r="111"/>
     <row r="112" ht="24" customHeight="1" s="69"/>
+    <row r="113"/>
     <row r="114" ht="24" customHeight="1" s="69"/>
+    <row r="115"/>
+    <row r="116"/>
     <row r="117" ht="36" customHeight="1" s="69"/>
     <row r="118" ht="24" customHeight="1" s="69"/>
     <row r="119" ht="84" customHeight="1" s="69"/>
@@ -2010,39 +2056,64 @@
     <row r="122" ht="24" customHeight="1" s="69"/>
     <row r="123" ht="24" customHeight="1" s="69"/>
     <row r="124" ht="48" customHeight="1" s="69"/>
+    <row r="125"/>
     <row r="126" ht="36" customHeight="1" s="69"/>
+    <row r="127"/>
     <row r="128" ht="24" customHeight="1" s="69"/>
     <row r="129" ht="24" customHeight="1" s="69"/>
     <row r="130" ht="48" customHeight="1" s="69"/>
     <row r="131" ht="24" customHeight="1" s="69"/>
+    <row r="132"/>
     <row r="133" ht="36" customHeight="1" s="69"/>
     <row r="134"/>
+    <row r="135"/>
+    <row r="136"/>
     <row r="137" ht="24" customHeight="1" s="69"/>
     <row r="138" ht="24" customHeight="1" s="69"/>
     <row r="139" ht="36" customHeight="1" s="69"/>
     <row r="140" ht="24" customHeight="1" s="69"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
     <row r="145" ht="36" customHeight="1" s="69"/>
     <row r="146" ht="36" customHeight="1" s="69"/>
     <row r="147" ht="36" customHeight="1" s="69"/>
+    <row r="148"/>
     <row r="149" ht="24" customHeight="1" s="69"/>
     <row r="150" ht="24" customHeight="1" s="69"/>
+    <row r="151"/>
     <row r="152" ht="24" customHeight="1" s="69"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
     <row r="158" ht="48" customHeight="1" s="69"/>
     <row r="159" ht="24" customHeight="1" s="69"/>
     <row r="160" ht="48" customHeight="1" s="69"/>
+    <row r="161"/>
     <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
     <row r="165" ht="36" customHeight="1" s="69"/>
     <row r="166" ht="24" customHeight="1" s="69"/>
     <row r="167" ht="36" customHeight="1" s="69"/>
+    <row r="168"/>
     <row r="169" ht="24" customHeight="1" s="69"/>
     <row r="170"/>
+    <row r="171"/>
     <row r="172"/>
+    <row r="173"/>
     <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
     <row r="177"/>
     <row r="178"/>
     <row r="179"/>
     <row r="180"/>
     <row r="181"/>
+    <row r="182"/>
     <row r="183"/>
     <row r="184"/>
     <row r="185"/>
@@ -2103,7 +2174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4.7109375" customWidth="1" style="69" min="1" max="1"/>
@@ -2135,6 +2206,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="1" t="inlineStr">
         <is>
@@ -2149,6 +2221,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="43" t="inlineStr">
         <is>
@@ -2519,7 +2592,7 @@
       <c r="A34" s="9" t="n"/>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">   kao Stamford BCI164C ili ekvivalent</t>
+          <t xml:space="preserve">    kao Stamford BCI164C U IZVEDBI SA PMG ILI AREP/AUX POBUDOM, ili ekvivalent — standardna SHUNT izvedba NIJE prihvatljiva (v. zahtjev za pobudu iznad)</t>
         </is>
       </c>
       <c r="C34" s="9" t="n"/>
@@ -2795,6 +2868,7 @@
         <v/>
       </c>
     </row>
+    <row r="56"/>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
@@ -2815,7 +2889,7 @@
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="61" t="inlineStr">
         <is>
-          <t>Opšte napomene  Nosivost poda kontejnera je 10,00 kN/m² (ukupno stalno + korisno opterećenje, prema statičkom proračunu tipskog kontejnera K3):Napomena uz Tačku 4: DEA se ugrađuje u postojeći kontejner na lokaciji, u "inside skid" izvedbi (agregat na zajedničkom nosivom skid-okviru, bez vlastitog vanjskog kućišta, jer funkciju kućišta preuzima kontejner). Referentna izvedba data je u Prilogu III</t>
+          <t>Opšte napomene  NOSIVOST PODA KONTEJNERA: mjerodavna projektna vrijednost je 2,00 kN/m² prema Projektnom zadatku. Ranije navedenih 10,00 kN/m² preuzeto je iz statičkog proračuna tipskog kontejnera K3, a na ovoj lokaciji ugrađen je kontejner tipa K2, pa ta vrijednost NIJE mjerodavna. Agregat (385 kg mokro na 0,96 m² = 3,93 kN/m²) i pun spremnik (≈590 kg na 0,63 m² = 9,2 kN/m²) oba prekoračuju projektnu nosivost, zbog čega je OBAVEZAN čelični ram/roštilj za raznošenje opterećenja ispod skida I ispod tankvane, sa prenosom opterećenja na temeljnu konstrukciju, dokazan statičkim proračunom iz Tačke 4.4.Napomena uz Tačku 4: DEA se ugrađuje u postojeći kontejner na lokaciji, u "inside skid" izvedbi (agregat na zajedničkom nosivom skid-okviru, bez vlastitog vanjskog kućišta, jer funkciju kućišta preuzima kontejner). Referentna izvedba data je u Prilogu III</t>
         </is>
       </c>
       <c r="C58" s="9" t="n"/>
@@ -2904,7 +2978,8 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Isporuka, montaža i povezivanje dvoplašnog spremnika dizel goriva zapremine 500 l (0,5 m³), izrađenog od čeličnog lima, sa svim spojnim priborom, cjevovodima i armaturama.</t>
+          <t>Isporuka, montaža i povezivanje dvoplašnog spremnika dizel goriva zapremine 500 l (0,5 m³), izrađenog od čeličnog lima, sa svim spojnim priborom, cjevovodima i armaturama.
+ - referentne dimenzije spremnika 1050 × 600 × 1310 mm, masa prazan 170 kg (pun ≈590 kg); smještaj uz SJEVERNI zid kontejnera u tankvani iz Tačke 4.3, prema crtežu M-01</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3074,7 +3149,9 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>OBAVEZAN statički proračun nosivosti podne konstrukcije postojećeg kontejnera, ovjeren od strane ovlaštenog inženjera, te izvođenje OJAČANJA poda ukoliko proračun pokaže da postojeća konstrukcija ne prihvata opterećenje. Ojačanje obuhvata izradu i ugradnju čeličnog roštilja za raznоšenje opterećenja skida agregata i punog spremnika goriva od 500 l, sa prenosom opterećenja na temeljnu konstrukciju kontejnera, uključujući antikorozivnu zaštitu i sav spojni materijal. Podna konstrukcija tipskog kontejnera K3 proračunata je na ukupno opterećenje (stalno + korisno) od 10,00 kN/m², sa raspoloživim budžetom korisnog opterećenja temelja od cca 5,0 kN/m² na zoni od cca 5,8 m² (prema statičkom proračunu kontejnera K3), dok masa skida i punog spremnika od 500 l (cca 1.150–1.350 kg na 2–3 m²) NE prelazi ove vrijednosti, zbog čega se ojačanje NE očekuje kao neophodno — ali ostaje OBAVEZNA provjera statičkim proračunom prije izvođenja. Zapremina spremnika se ne umanjuje.</t>
+          <t>OBAVEZAN statički proračun nosivosti podne konstrukcije postojećeg kontejnera, ovjeren od strane ovlaštenog inženjera, te izvođenje OJAČANJA poda. Ojačanje obuhvata izradu i ugradnju čeličnog roštilja/rama za raznošenje opterećenja ISPOD SKIDA AGREGATA I ISPOD TANKVANE SA SPREMNIKOM, sa prenosom opterećenja na temeljnu konstrukciju kontejnera, uključujući antikorozivnu zaštitu i sav spojni materijal.
+OBRAZLOŽENJE: mjerodavna projektna nosivost poda je 2,00 kN/m² prema Projektnom zadatku. Agregat daje 3,93 kN/m² (385 kg mokro na 0,96 m²), a pun spremnik 9,2 kN/m² (≈590 kg na 0,63 m²) — oba prekoračuju projektnu vrijednost, pa je ojačanje NEOPHODNO, a ne uslovno. Ranija formulacija se pozivala na proračun tipskog kontejnera K3 (10,00 kN/m²), koji NIJE mjerodavan jer je na ovoj lokaciji ugrađen kontejner tipa K2.
+Zapremina spremnika se ne umanjuje.</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -3124,7 +3201,8 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Izrada i montaža limenog kanala P ≈ 6 m² za odvod toplog zraka sa agregata, od pocinčanog lima d=1 mm, sa prirubnicama 30 × 1,5 mm, komplet sa fazonskim komadima i ovjesnim priborom.</t>
+          <t>Izrada i montaža limenog kanala P ≈ 6 m² za odvod toplog zraka sa agregata, od pocinčanog lima d=1 mm, sa prirubnicama 30 × 1,5 mm, komplet sa fazonskim komadima i ovjesnim priborom.
+RASPORED (OBAVEZNO, prema crtežu M-01): kanal se vodi najkraćim putem od radijatora kroz ZAPADNI zid kontejnera do izlazne žaluzine iz Tačke 4.7.</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -3149,7 +3227,8 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i montaža fiksne žaluzine na kraju kanala za odvod toplog zraka, dimenzija 600 × 600 mm, sa zaštitnom mrežicom, komplet sa montažnim materijalom.</t>
+          <t>Isporuka i montaža fiksne žaluzine na kraju kanala za odvod toplog zraka, dimenzija 600 × 600 mm, sa zaštitnom mrežicom, komplet sa montažnim materijalom.
+RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u ZAPADNI zid kontejnera, na osi radijatora agregata. Topli zrak se NE smije izbacivati prema SJEVERNOJ strani, gdje se nalaze postojeći vanjski ormari ICC330-H1 i MTS9302.</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -3174,7 +3253,8 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i montaža vanjske fiksne žaluzine za dovod svježeg zraka, dimenzija 500 × 700 mm, sa zaštitnom mrežicom. Žaluzine postaviti tako da se spriječi ulaz vode u kontejner prilikom padavina.</t>
+          <t>Isporuka i montaža vanjske fiksne žaluzine za dovod svježeg zraka, dimenzija 500 × 700 mm, sa zaštitnom mrežicom. Žaluzine postaviti tako da se spriječi ulaz vode u kontejner prilikom padavina.
+RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u JUŽNI zid kontejnera, na istočnom kraju, sa donjom ivicom na cca 0,30 m od poda. Prostorna udaljenost od izduva i od odušne cijevi spremnika ≥3 m. Nije dozvoljeno izvesti dovod zraka kroz ulazna vrata.</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -3199,7 +3279,8 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i montaža aksijalnog ventilatora za prinudnu ventilaciju prostora agregata, kapaciteta 1200 m³/h, Ø315 mm, sa termostatskim upravljanjem. Ventilator spojiti sa komandnim ormarom agregata tako da se prilikom uključenja agregata vrši i direktno uključenje ventilatora. Minimalna potrebna ventilacija prostora iznosi 120 m³/h (6 izmjena zraka na sat).</t>
+          <t>Isporuka i montaža aksijalnog ventilatora za prinudnu ventilaciju prostora agregata, kapaciteta 1200 m³/h, Ø315 mm, sa termostatskim upravljanjem. Ventilator spojiti sa komandnim ormarom agregata tako da se prilikom uključenja agregata vrši i direktno uključenje ventilatora. Minimalna potrebna ventilacija prostora iznosi 120 m³/h (6 izmjena zraka na sat).
+RASPORED (OBAVEZNO, prema crtežu M-01): ventilator se ugrađuje u ISTOČNI zid kontejnera, u gornjoj zoni (donja ivica cca 1,75 m), sjeverno od ulaznih vrata.</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -3249,7 +3330,8 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i montaža sistema za odvod izduvnih gasova: čelična cijev NO 50 mm sa ispušnim loncem, izvedena izvan kontejnera i završena oboreno prema zemlji u obliku lule. Na kraju izduvne cijevi postaviti HVATAČ ISKRI. Komplet sa elastičnim umetkom, lukovima i montažnim materijalom.</t>
+          <t>Isporuka i montaža sistema za odvod izduvnih gasova: čelična cijev NO 50 mm sa ispušnim loncem, izvedena izvan kontejnera i završena oboreno prema zemlji u obliku lule. Na kraju izduvne cijevi postaviti HVATAČ ISKRI. Komplet sa elastičnim umetkom, lukovima i montažnim materijalom.
+IZMJENA — PREČNIK I TRASA: usvaja se DN 65 umjesto NO 50 (pri NO 50 brzina izduvnih gasova je 33 m/s, iznad uobičajenih 30 m/s; protutlak je zadovoljen u oba slučaja). Trasa: fleksibilni spoj i prigušivač neposredno iza motora, uspon uz ZAPADNI zid kontejnera, završetak IZNAD KROVA usmjeren naviše, sa hvatačem iskri, na prostornoj udaljenosti ≥3 m od usisne žaluzine i od odušne cijevi spremnika (prema crtežu M-01).</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -3442,129 +3524,116 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="96" t="inlineStr">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>4.19</t>
+        </is>
+      </c>
+      <c r="F91" s="8">
+        <f>IF(AND(D91&lt;&gt;"",E91&lt;&gt;""),D91*E91,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>Isporuka i ugradnja protupožarnog (sigurnosnog) ventila na izlaznom vodu goriva iz spremnika, sa termičkim okidanjem (topljivi osigurač) ili solenoidnom izvedbom, koji zatvara dovod goriva pri požaru i pri aktiviranju tastera EMERGENCY STOP. Komplet sa nosačem, spojnim materijalom, uvezivanjem u sistem detekcije požara i funkcionalnim ispitivanjem.</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" s="8" t="n"/>
+      <c r="F92" s="8">
+        <f>IF(AND(D92&lt;&gt;"",E92&lt;&gt;""),D92*E92,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>Isporuka, ugradnja i parametriranje blokade ventilacije pri aktiviranju automatskog gašenja: pri detekciji požara i aktivaciji uređaja za gašenje automatski se zaustavlja agregat, isključuje aksijalni ventilator prostora i zatvaraju se motorne žaluzine dovoda i odvoda zraka, kako sredstvo za gašenje ne bi bilo odneseno strujom zraka. Uključene motorne klapne na usisnoj i izlaznoj žaluzini, upravljački modul, kablovanje i funkcionalno ispitivanje.</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8">
+        <f>IF(AND(D93&lt;&gt;"",E93&lt;&gt;""),D93*E93,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1" s="69">
+      <c r="A94" s="96" t="inlineStr">
         <is>
           <t>UKUPNO 4 — AGREGAT ZA MONTAŽU U KONTEJNER:</t>
         </is>
       </c>
-      <c r="B91" s="16" t="n"/>
-      <c r="C91" s="16" t="n"/>
-      <c r="D91" s="16" t="n"/>
-      <c r="E91" s="17" t="n"/>
-      <c r="F91" s="10">
-        <f>SUM(F59:F90)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="B94" s="16" t="n"/>
+      <c r="C94" s="16" t="n"/>
+      <c r="D94" s="16" t="n"/>
+      <c r="E94" s="17" t="n"/>
+      <c r="F94" s="10">
+        <f>SUM(F59:F93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="24" customHeight="1" s="69"/>
+    <row r="96" ht="36" customHeight="1" s="69">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>ELEKTROMONTAŽNI RADOVI</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-    </row>
-    <row r="94" ht="24" customHeight="1" s="69">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>5.1</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Iskop rova dimenzija 0,40 × 0,80 m u zemlji IV-V kategorije za polaganje elektroenergetskih kablova i uzemljivačke trake, sa zatrpavanjem zemljom od iskopa te raščišćavanjem i planiranjem trase. Obračun po ostvarenom m1.</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>m1</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="E94" s="8" t="n"/>
-      <c r="F94" s="8">
-        <f>IF(AND(D94&lt;&gt;"",E94&lt;&gt;""),D94*E94,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="95" ht="24" customHeight="1" s="69">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>5.2</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Isporuka i polaganje alkaten PEHD cijevi Ø50 za uvlačenje napojnog energetskog kabla, DC solarnih kablova i kabla za daljinski nadzor. Na cijevi položiti upozoravajuću PVC traku "PAŽNJA ENERGETSKI KABEL". 3 cijevi × 15,00 m</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="E95" s="8" t="n"/>
-      <c r="F95" s="8">
-        <f>IF(AND(D95&lt;&gt;"",E95&lt;&gt;""),D95*E95,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="36" customHeight="1" s="69">
-      <c r="A96" s="6" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Isporuka i polaganje vruće pocinčane uzemljivačke trake Fe/Zn 25×4 mm (presjek min. 100 mm², debljina min. 2,5 mm), na dubini od 1,00 m obzirom da se radi o planinskoj lokaciji (izbjegavanje efekta zaleđivanja tla), sa svim radovima na povezivanju na postojeći prstenasti uzemljivač radi izjednačenja potencijala.</t>
-        </is>
-      </c>
-      <c r="C96" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="E96" s="8" t="n"/>
-      <c r="F96" s="8">
-        <f>IF(AND(D96&lt;&gt;"",E96&lt;&gt;""),D96*E96,"")</f>
-        <v/>
-      </c>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
+      <c r="E96" s="5" t="n"/>
+      <c r="F96" s="5" t="n"/>
     </row>
     <row r="97" ht="24" customHeight="1" s="69">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i montaža FeZn 60×60 mm ukrsnih komada za povezivanje uzemljivačke trake na postojeći sistem uzemljenja i na nosive konstrukcije FN panela.</t>
+          <t>Iskop rova dimenzija 0,40 × 0,80 m u zemlji IV-V kategorije za polaganje elektroenergetskih kablova i uzemljivačke trake, sa zatrpavanjem zemljom od iskopa te raščišćavanjem i planiranjem trase. Obračun po ostvarenom m1.</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>kom</t>
+          <t>m1</t>
         </is>
       </c>
       <c r="D97" s="6" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E97" s="8" t="n"/>
       <c r="F97" s="8">
@@ -3575,21 +3644,21 @@
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i polaganje veza na dionici hibridni sistem — DEA:</t>
+          <t>Isporuka i polaganje alkaten PEHD cijevi Ø50 za uvlačenje napojnog energetskog kabla, DC solarnih kablova i kabla za daljinski nadzor. Na cijevi položiti upozoravajuću PVC traku "PAŽNJA ENERGETSKI KABEL". 3 cijevi × 15,00 m</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D98" s="6" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E98" s="8" t="n"/>
       <c r="F98" s="8">
@@ -3598,46 +3667,85 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="n"/>
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - energetski kabl dužine do 15 m, tip NYY-J 5×6 mm²</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="n"/>
-      <c r="D99" s="9" t="n"/>
-      <c r="E99" s="9" t="n"/>
-      <c r="F99" s="9" t="n"/>
+          <t>Isporuka i polaganje vruće pocinčane uzemljivačke trake Fe/Zn 25×4 mm (presjek min. 100 mm², debljina min. 2,5 mm), na dubini od 1,00 m obzirom da se radi o planinskoj lokaciji (izbjegavanje efekta zaleđivanja tla), sa svim radovima na povezivanju na postojeći prstenasti uzemljivač radi izjednačenja potencijala.</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="E99" s="8" t="n"/>
+      <c r="F99" s="8">
+        <f>IF(AND(D99&lt;&gt;"",E99&lt;&gt;""),D99*E99,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="9" t="n"/>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>5.4</t>
+        </is>
+      </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - signalni kabl dužine do 15 m, tip J-Y(ST)Y 4×2×0,6 mm²</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="n"/>
-      <c r="D100" s="9" t="n"/>
-      <c r="E100" s="9" t="n"/>
-      <c r="F100" s="9" t="n"/>
+          <t>Isporuka i montaža FeZn 60×60 mm ukrsnih komada za povezivanje uzemljivačke trake na postojeći sistem uzemljenja i na nosive konstrukcije FN panela.</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>kom</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8">
+        <f>IF(AND(D100&lt;&gt;"",E100&lt;&gt;""),D100*E100,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="9" t="n"/>
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - komunikacioni Ethernet kabl dužine do 15 m, tip STP Cat5</t>
-        </is>
-      </c>
-      <c r="C101" s="9" t="n"/>
-      <c r="D101" s="9" t="n"/>
-      <c r="E101" s="9" t="n"/>
-      <c r="F101" s="9" t="n"/>
+          <t>Isporuka i polaganje veza na dionici hibridni sistem — DEA:</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="8" t="n"/>
+      <c r="F101" s="8">
+        <f>IF(AND(D101&lt;&gt;"",E101&lt;&gt;""),D101*E101,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="102" ht="36" customHeight="1" s="69">
       <c r="A102" s="9" t="n"/>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Kablovi se polažu uvlačenjem u PEHD cijevi/bužire i u metalne kanale, komplet sa montažnim materijalom, spajanjem na obje strane, bušenjem prodora na kontejneru, ugradnjom uvodnica i zaštitnog lima. Obavezna obrada svih prodora sa aspekta sigurnosti, toplinske izolacije (pur pjena, armaflex) i estetike.</t>
+          <t xml:space="preserve"> - energetski kabl dužine do 15 m, tip NYY-J 5×6 mm²</t>
         </is>
       </c>
       <c r="C102" s="9" t="n"/>
@@ -3646,35 +3754,22 @@
       <c r="F102" s="9" t="n"/>
     </row>
     <row r="103" ht="36" customHeight="1" s="69">
-      <c r="A103" s="6" t="inlineStr">
-        <is>
-          <t>5.6</t>
-        </is>
-      </c>
+      <c r="A103" s="9" t="n"/>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Isporuka i montaža NOVOG GLAVNOG RAZVODNOG ORMARA (GRO) — AC RAZVODNA SEKCIJA, za ugradnju u postojeći kontejner. Ormar služi kao zajednička AC razvodna kutija za agregat (DEA), ispravljački sistem (Huawei PowerCube 1000) i ostalu AC opremu kontejnera; DC/solarni razvod je izveden odvojeno, u zasebnom PVDB ormaru prema Tački 1.6 LOT-a 1 (AC i DC krugovi se ne miješaju u istom ormaru). Ormar zidni sa nosačima, orijentacionih dimenzija 0,60 × 0,25 × 0,80 m (Š×D×V), mehaničke zaštite min. IP66, zabravljen bravom sa višestrukim zaključavanjem, kao Schrack ili ekvivalent.</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8">
-        <f>IF(AND(D103&lt;&gt;"",E103&lt;&gt;""),D103*E103,"")</f>
-        <v/>
-      </c>
+          <t xml:space="preserve"> - signalni kabl dužine do 15 m, tip J-Y(ST)Y 4×2×0,6 mm²</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
     </row>
     <row r="104" ht="36" customHeight="1" s="69">
       <c r="A104" s="9" t="n"/>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Sa donje strane ormara obezbijediti prostor za uvod i smještaj kablova sa PG uvodnicama prema dimenzijama kablova, opremljen stezaljkama, elementima za uzemljenje i sabirnicama, komplet ožičeno, sa uključenim ožičenjem preostalog prostora za naknadna proširenja (min. 30 % rezerve).</t>
+          <t xml:space="preserve"> - komunikacioni Ethernet kabl dužine do 15 m, tip STP Cat5</t>
         </is>
       </c>
       <c r="C104" s="9" t="n"/>
@@ -3686,7 +3781,7 @@
       <c r="A105" s="9" t="n"/>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>AC RAZVOD — AGREGAT I ISPRAVLJAČI:</t>
+          <t>Kablovi se polažu uvlačenjem u PEHD cijevi/bužire i u metalne kanale, komplet sa montažnim materijalom, spajanjem na obje strane, bušenjem prodora na kontejneru, ugradnjom uvodnica i zaštitnog lima. Obavezna obrada svih prodora sa aspekta sigurnosti, toplinske izolacije (pur pjena, armaflex) i estetike.</t>
         </is>
       </c>
       <c r="C105" s="9" t="n"/>
@@ -3695,22 +3790,35 @@
       <c r="F105" s="9" t="n"/>
     </row>
     <row r="106" ht="24" customHeight="1" s="69">
-      <c r="A106" s="9" t="n"/>
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>5.6</t>
+        </is>
+      </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 1 kom 4p tropoložajna sklopka za odabir izvora napajanja, izvedbe 1-0-2, 63 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN). Položaje obilježiti: 1-"hibridni sistem", 0-"isključeno", 2-"agregat"</t>
-        </is>
-      </c>
-      <c r="C106" s="9" t="n"/>
-      <c r="D106" s="9" t="n"/>
-      <c r="E106" s="9" t="n"/>
-      <c r="F106" s="9" t="n"/>
+          <t>Isporuka i montaža NOVOG GLAVNOG RAZVODNOG ORMARA (GRO) — AC RAZVODNA SEKCIJA, za ugradnju u postojeći kontejner. Ormar služi kao zajednička AC razvodna kutija za agregat (DEA), ispravljački sistem (Huawei ICC330-H1 + MTS9302 ili kompatibilan) i ostalu AC opremu kontejnera; DC/solarni razvod je izveden odvojeno, u zasebnom PVDB ormaru prema Tački 1.6 LOT-a 1 (AC i DC krugovi se ne miješaju u istom ormaru). Ormar zidni sa nosačima, orijentacionih dimenzija 0,60 × 0,25 × 0,80 m (Š×D×V), mehaničke zaštite min. IP66, zabravljen bravom sa višestrukim zaključavanjem, kao Schrack ili ekvivalent.</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="8" t="n"/>
+      <c r="F106" s="8">
+        <f>IF(AND(D106&lt;&gt;"",E106&lt;&gt;""),D106*E106,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="107" ht="24" customHeight="1" s="69">
       <c r="A107" s="9" t="n"/>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 1 kom 3p dvopoložajna sklopka za isključenje napojnog kruga, izvedbe 0-1, 63 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)</t>
+          <t>Sa donje strane ormara obezbijediti prostor za uvod i smještaj kablova sa PG uvodnicama prema dimenzijama kablova, opremljen stezaljkama, elementima za uzemljenje i sabirnicama, komplet ožičeno, sa uključenim ožičenjem preostalog prostora za naknadna proširenja (min. 30 % rezerve).</t>
         </is>
       </c>
       <c r="C107" s="9" t="n"/>
@@ -3722,7 +3830,7 @@
       <c r="A108" s="9" t="n"/>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 3 kom 1p automatski prekidač, C, 32 A, 10 kA za zaštitu napajanja preko DEA</t>
+          <t>AC RAZVOD — AGREGAT I ISPRAVLJAČI:</t>
         </is>
       </c>
       <c r="C108" s="9" t="n"/>
@@ -3734,10 +3842,7 @@
       <c r="A109" s="9" t="n"/>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 1 kom odvodnik prenapona AC, 4p, katodni, min. 40 kA / 275 V, sa signalizacijom za daljinsko očitanje stanja i uvezanim statusom sa kontrolerom agregata (DIG IN)
- - 1 kom 4p zaštitna strujna sklopka (RCD) 63 A / 300 mA, S-tip (selektivna), za zaštitu cjelokupnog napojnog kruga iza sklopke izvora
- - 2 kom 1p+N zaštitna strujna sklopka sa prekostrujnom zaštitom (RCBO) 16 A / 30 mA, tip A, za utičnice i rasvjetu kontejnera
-NAPOMENA (obavezno): agregat je SHUNT pobude i prema tehničkom listu proizvođača ima deklarisanu sposobnost trajne struje kratkog spoja 0 %, zbog čega SAMO prekostrujna zaštita NE MOŽE ostvariti automatsko isključenje u vremenu zahtijevanom prema IEC 60364-4-41 (0,4 s za 230 V). Zaštita zaštitnom strujnom sklopkom je stoga OBAVEZNA. Sistem uzemljenja je TN-S sa jedinstvenom tačkom spajanja N i PE u ovom ormaru; otpor uzemljenja ≤10 Ω.</t>
+          <t xml:space="preserve"> - 1 kom 4p tropoložajna sklopka za odabir izvora napajanja, izvedbe 1-0-2, 63 A, sa uvezanim statusom slobodnog kontakta sa kontrolerom agregata (DIG IN). Položaje obilježiti: 1-"hibridni sistem", 0-"isključeno", 2-"agregat"</t>
         </is>
       </c>
       <c r="C109" s="9" t="n"/>
@@ -3749,7 +3854,7 @@
       <c r="A110" s="9" t="n"/>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 1 kom 3p automatski prekidač, C, 32 A, 10 kA, za AC napajanje ispravljačkog sistema (Huawei PowerCube 1000)</t>
+          <t xml:space="preserve"> - 1 kom 3p dvopoložajna sklopka za isključenje napojnog kruga, izvedbe 0-1, 63 A, sa pomoćnim kontaktom za uvezivanje statusa sa kontrolerom agregata (DIG IN)</t>
         </is>
       </c>
       <c r="C110" s="9" t="n"/>
@@ -3761,7 +3866,7 @@
       <c r="A111" s="9" t="n"/>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - 2 kom 1p automatski prekidač, C, 16 A, sa rezervom za ostalu AC opremu kontejnera (rasvjeta, utičnice, klima i sl.) i buduća proširenja</t>
+          <t xml:space="preserve"> - 3 kom 1p automatski prekidač, C, 32 A, 10 kA za zaštitu napajanja preko DEA</t>
         </is>
       </c>
       <c r="C111" s="9" t="n"/>
@@ -3773,7 +3878,10 @@
       <c r="A112" s="9" t="n"/>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>NAPOMENA — DC/SOLARNI RAZVOD NIJE DIO OVOG ORMARA:</t>
+          <t xml:space="preserve"> - 1 kom odvodnik prenapona AC, KOMBINOVANI TIP 1 + 2 prema EN 61643-11, Iimp ≥12,5 kA (10/350 µs) po polu, Up ≤1,5 kV, 4p, sa signalizacijom za daljinsko očitanje stanja i uvezanim statusom sa kontrolerom agregata. Objekat ima vanjski sistem zaštite od munje (antenski stub h=38 m), pa odvodnik tipa 2 sam po sebi NIJE dovoljan prema EN 62305-4.
+ - 1 kom 4p zaštitna strujna sklopka (RCD) 63 A / 300 mA, S-tip (selektivna), za zaštitu cjelokupnog napojnog kruga iza sklopke izvora
+ - 2 kom 1p+N zaštitna strujna sklopka sa prekostrujnom zaštitom (RCBO) 16 A / 30 mA, tip A, za utičnice i rasvjetu kontejnera
+NAPOMENA (obavezno): agregat je SHUNT pobude i prema tehničkom listu proizvođača ima deklarisanu sposobnost trajne struje kratkog spoja 0 %, zbog čega SAMO prekostrujna zaštita NE MOŽE ostvariti automatsko isključenje u vremenu zahtijevanom prema IEC 60364-4-41 (0,4 s za 230 V). Zaštita zaštitnom strujnom sklopkom je stoga OBAVEZNA. Sistem uzemljenja je TN-S sa jedinstvenom tačkom spajanja N i PE u ovom ormaru; otpor uzemljenja ≤10 Ω.</t>
         </is>
       </c>
       <c r="C112" s="9" t="n"/>
@@ -3785,7 +3893,7 @@
       <c r="A113" s="9" t="n"/>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - DC rastavljač, osigurači nizova FN panela i DC odvodnik prenapona (tip 2) smješteni su u zasebnom PVDB ormaru prema Tački 1.6 (LOT 1), fizički odvojenom od ovog GRO-a, radi razdvajanja AC i DC krugova u posebnim kućištima.</t>
+          <t xml:space="preserve"> - 1 kom 3p automatski prekidač, C, 32 A, 10 kA, za AC napajanje ispravljačkog sistema (Huawei ICC330-H1 + MTS9302 ili kompatibilan)</t>
         </is>
       </c>
       <c r="C113" s="9" t="n"/>
@@ -3795,7 +3903,11 @@
     </row>
     <row r="114">
       <c r="A114" s="9" t="n"/>
-      <c r="B114" s="7" t="n"/>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - 2 kom 1p automatski prekidač, C, 16 A, sa rezervom za ostalu AC opremu kontejnera (rasvjeta, utičnice, klima i sl.) i buduća proširenja</t>
+        </is>
+      </c>
       <c r="C114" s="9" t="n"/>
       <c r="D114" s="9" t="n"/>
       <c r="E114" s="9" t="n"/>
@@ -3805,7 +3917,7 @@
       <c r="A115" s="9" t="n"/>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>Napomena: Sve metalne mase ormara koje u normalnom radu nisu pod naponom povezati na sabirnice za izjednačenje potencijala. Uvodi kablova brtvljeni uvodnicama. Izraditi i pričvrstiti natpisne pločice sa prednje strane ormara, gravirano: "GRO AC — AGREGAT/ISPRAVLJAČI — BS SJEDNICA" i oznaka W012 "OPASAN NAPON" u skladu sa EN ISO 7010.</t>
+          <t>NAPOMENA — DC/SOLARNI RAZVOD NIJE DIO OVOG ORMARA:</t>
         </is>
       </c>
       <c r="C115" s="9" t="n"/>
@@ -3814,132 +3926,150 @@
       <c r="F115" s="9" t="n"/>
     </row>
     <row r="116" ht="24" customHeight="1" s="69">
-      <c r="A116" s="6" t="inlineStr">
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - DC rastavljač, osigurači nizova FN panela i DC odvodnik prenapona (tip 2) smješteni su u zasebnom PVDB ormaru prema Tački 1.6 (LOT 1), fizički odvojenom od ovog GRO-a, radi razdvajanja AC i DC krugova u posebnim kućištima.</t>
+        </is>
+      </c>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+    </row>
+    <row r="117" ht="36" customHeight="1" s="69">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>Napomena: Sve metalne mase ormara koje u normalnom radu nisu pod naponom povezati na sabirnice za izjednačenje potencijala. Uvodi kablova brtvljeni uvodnicama. Izraditi i pričvrstiti natpisne pločice sa prednje strane ormara, gravirano: "GRO AC — AGREGAT/ISPRAVLJAČI — BS SJEDNICA" i oznaka W012 "OPASAN NAPON" u skladu sa EN ISO 7010.</t>
+        </is>
+      </c>
+      <c r="C118" s="9" t="n"/>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
       </c>
-      <c r="B116" s="7" t="inlineStr">
+      <c r="B119" s="97" t="inlineStr">
         <is>
           <t>Uvezivanje kontrolera DEA sa Huawei kontrolno-upravljačkim sistemom (modul GIM01C1) i sa razvodnim ormarom signalizacije (ROS), te parametriranje kriterija automatskog starta po stanju napunjenosti baterija (SoC).</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D119" t="n">
         <v>1</v>
       </c>
-      <c r="E116" s="8" t="n"/>
-      <c r="F116" s="8">
-        <f>IF(AND(D116&lt;&gt;"",E116&lt;&gt;""),D116*E116,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="36" customHeight="1" s="69">
-      <c r="A117" s="6" t="inlineStr">
+      <c r="F119" s="8">
+        <f>IF(AND(D119&lt;&gt;"",E119&lt;&gt;""),D119*E119,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
         <is>
           <t>5.8</t>
         </is>
       </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="B120" s="7" t="inlineStr">
         <is>
           <t>PROVJERA UZEMLJENJA I ELEKTRIČNIH INSTALACIJA sa izdavanjem stručnog nalaza ovlaštene kuće: mjerenje otpora uzemljenja i neprekidnosti zaštitnog vodiča, mjerenje otpora izolacije, ispitivanje zaštite od indirektnog dodira, provjera izjednačenja potencijala, funkcionalno ispitivanje automatskog starta DEA. Otpor uzemljenja mora zadovoljiti zahtjeve Projektnog zadatka.</t>
         </is>
       </c>
-      <c r="C117" s="6" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D120" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E117" s="8" t="n"/>
-      <c r="F117" s="8">
-        <f>IF(AND(D117&lt;&gt;"",E117&lt;&gt;""),D117*E117,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
+      <c r="E120" s="8" t="n"/>
+      <c r="F120" s="8">
+        <f>IF(AND(D120&lt;&gt;"",E120&lt;&gt;""),D120*E120,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
       </c>
-      <c r="B118" s="7" t="inlineStr">
+      <c r="B121" s="7" t="inlineStr">
         <is>
           <t>Ostali sitni montažni i potrošni materijal.</t>
         </is>
       </c>
-      <c r="C118" s="6" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>paušal</t>
         </is>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D121" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E118" s="8" t="n"/>
-      <c r="F118" s="8">
-        <f>IF(AND(D118&lt;&gt;"",E118&lt;&gt;""),D118*E118,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="15" t="inlineStr">
-        <is>
-          <t>UKUPNO 5 — ELEKTROMONTAŽNI RADOVI:</t>
-        </is>
-      </c>
-      <c r="B119" s="16" t="n"/>
-      <c r="C119" s="16" t="n"/>
-      <c r="D119" s="16" t="n"/>
-      <c r="E119" s="17" t="n"/>
-      <c r="F119" s="10">
-        <f>SUM(F94:F118)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA (DO POTPUNE GOTOVOSTI)</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="5" t="n"/>
-      <c r="F121" s="5" t="n"/>
+      <c r="E121" s="8" t="n"/>
+      <c r="F121" s="8">
+        <f>IF(AND(D121&lt;&gt;"",E121&lt;&gt;""),D121*E121,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="122" ht="36" customHeight="1" s="69">
-      <c r="A122" s="9" t="n"/>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Napomena uz Tačku 6: LOT 2 obuhvata usluge montaže i uvezivanja sistema DO POTPUNE GOTOVOSTI i funkcionalnosti, uključujući sve radove, materijal i usluge neophodne za predaju sistema u ispravnom i funkcionalnom stanju, bez obzira da li su izričito navedeni u pojedinačnim stavkama.</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="n"/>
-      <c r="D122" s="9" t="n"/>
-      <c r="E122" s="9" t="n"/>
-      <c r="F122" s="9" t="n"/>
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>5.10</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>Snimanje postojećeg stanja i prevezivanje postojećih strujnih krugova na novi GRO iz Tačke 5.6. Obuhvata:
+ - snimanje i evidentiranje svih 7 postojećih strujnih krugova postojećeg razvoda, sa mjerenjem opterećenja i izradom jednopolne sheme zatečenog stanja
+ - prevezivanje krugova na odgovarajuće izvode novog GRO, sa označavanjem
+ - SIGNALNA RASVJETA PREPREKE antenskog stuba h=38 m (krug K7) izvodi se kao ZASEBAN NADZIRANI strujni krug, sa nadzorom prisustva napona i strujnim nadzorom ispravnosti svjetiljke, i dojavom ispada u sistem daljinskog nadzora — rasvjeta prepreke je trajno noćno opterećenje i ne smije biti isključena prilikom rekonfiguracije napajanja
+ - Ponuđač mjeri stvarnu snagu rasvjete prepreke i dostavlja je Kupcu radi provjere energetskog bilansa (Prilog I, Tačka 1)
+Komplet sa spojnim materijalom, oznakama, ispitivanjem i ažuriranom jednopolnom shemom izvedenog stanja.</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" s="8" t="n"/>
+      <c r="F122" s="8">
+        <f>IF(AND(D122&lt;&gt;"",E122&lt;&gt;""),D122*E122,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="123" ht="24" customHeight="1" s="69">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Puštanje u rad kompletnog sistema, funkcionalno testiranje automatskog starta DEA po kriteriju stanja baterija, testiranje prelaska izvora i 72-satni probni rad sa zapisom parametara.</t>
+          <t>Isporuka i ugradnja odvodnika prenapona za SIGNALNE i KOMUNIKACIONE VODOVE prema EN 61643-21: na signalnom kablu J-Y(ST)Y i na Ethernet vodu prema kontroleru agregata i sistemu daljinskog nadzora, na oba kraja dionice. Objekat ima vanjski sistem zaštite od munje i antenski stub h=38 m, pa je zaštita signalnih vodova obavezna prema EN 62305-4. Komplet sa nosačima, uzemljenjem odvodnika i ispitivanjem.</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -3957,312 +4087,358 @@
       </c>
     </row>
     <row r="124" ht="24" customHeight="1" s="69">
-      <c r="A124" s="6" t="inlineStr">
+      <c r="A124" s="15" t="inlineStr">
+        <is>
+          <t>UKUPNO 5 — ELEKTROMONTAŽNI RADOVI:</t>
+        </is>
+      </c>
+      <c r="B124" s="16" t="n"/>
+      <c r="C124" s="16" t="n"/>
+      <c r="D124" s="16" t="n"/>
+      <c r="E124" s="17" t="n"/>
+      <c r="F124" s="10">
+        <f>SUM(F97:F123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125"/>
+    <row r="126" ht="24" customHeight="1" s="69">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA (DO POTPUNE GOTOVOSTI)</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="n"/>
+      <c r="D126" s="5" t="n"/>
+      <c r="E126" s="5" t="n"/>
+      <c r="F126" s="5" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Napomena uz Tačku 6: LOT 2 obuhvata usluge montaže i uvezivanja sistema DO POTPUNE GOTOVOSTI i funkcionalnosti, uključujući sve radove, materijal i usluge neophodne za predaju sistema u ispravnom i funkcionalnom stanju, bez obzira da li su izričito navedeni u pojedinačnim stavkama.</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>Puštanje u rad kompletnog sistema, funkcionalno testiranje automatskog starta DEA po kriteriju stanja baterija, testiranje prelaska izvora i 72-satni probni rad sa zapisom parametara.</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" s="8" t="n"/>
+      <c r="F128" s="8">
+        <f>IF(AND(D128&lt;&gt;"",E128&lt;&gt;""),D128*E128,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
       </c>
-      <c r="B124" s="7" t="inlineStr">
+      <c r="B129" s="97" t="inlineStr">
         <is>
           <t>Uvezivanje kontrolera DEA u krovni sistem nadzora i upravljanja BH Telecom-a (SCADA — Ignition), sa isporukom licenciranog softverskog paketa, instalacijom u nadzornom centru, uvezivanjem do najbližeg switcha i testiranjem prosljeđivanja alarma.</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D129" t="n">
         <v>1</v>
       </c>
-      <c r="E124" s="8" t="n"/>
-      <c r="F124" s="8">
-        <f>IF(AND(D124&lt;&gt;"",E124&lt;&gt;""),D124*E124,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="6" t="inlineStr">
+      <c r="F129" s="8">
+        <f>IF(AND(D129&lt;&gt;"",E129&lt;&gt;""),D129*E129,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
       </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>Obuka osoblja Investitora (do 4 osobe) za rukovanje i osnovno održavanje sistema, u trajanju od min. 1 radnog dana.</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D130" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="8">
-        <f>IF(AND(D125&lt;&gt;"",E125&lt;&gt;""),D125*E125,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" ht="24" customHeight="1" s="69">
-      <c r="A126" s="6" t="inlineStr">
+      <c r="E130" s="8" t="n"/>
+      <c r="F130" s="8">
+        <f>IF(AND(D130&lt;&gt;"",E130&lt;&gt;""),D130*E130,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
       </c>
-      <c r="B126" s="7" t="inlineStr">
+      <c r="B131" s="97" t="inlineStr">
         <is>
           <t>Izrada dokumentacije izvedenog stanja za kompletan LOT 2 (elektro, mašinski i građevinski dio), u 3 štampana primjerka i u elektronskoj formi (PDF + izvorni DWG/DOCX).</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>kpl</t>
         </is>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D131" t="n">
         <v>1</v>
       </c>
-      <c r="E126" s="8" t="n"/>
-      <c r="F126" s="8">
-        <f>IF(AND(D126&lt;&gt;"",E126&lt;&gt;""),D126*E126,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="15" t="inlineStr">
+      <c r="F131">
+        <f>IF(AND(D131&lt;&gt;"",E131&lt;&gt;""),D131*E131,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="15" t="inlineStr">
         <is>
           <t>UKUPNO 6 — PUŠTANJE U RAD, OBUKA I DOKUMENTACIJA:</t>
         </is>
       </c>
-      <c r="B127" s="16" t="n"/>
-      <c r="C127" s="16" t="n"/>
-      <c r="D127" s="16" t="n"/>
-      <c r="E127" s="17" t="n"/>
-      <c r="F127" s="10">
-        <f>SUM(F123:F126)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="23" t="inlineStr">
+      <c r="B132" s="16" t="n"/>
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="n"/>
+      <c r="E132" s="17" t="n"/>
+      <c r="F132" s="10">
+        <f>SUM(F128:F131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="23" t="inlineStr">
         <is>
           <t>UKUPNO LOT 2 — DEA U POSTOJEĆEM KONTEJNERU (bez PDV-a):</t>
-        </is>
-      </c>
-      <c r="B129" s="16" t="n"/>
-      <c r="C129" s="16" t="n"/>
-      <c r="D129" s="16" t="n"/>
-      <c r="E129" s="17" t="n"/>
-      <c r="F129" s="14">
-        <f>F91+F119+F127</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="21" t="inlineStr">
-        <is>
-          <t>REKAPITULACIJA</t>
-        </is>
-      </c>
-      <c r="B131" s="16" t="n"/>
-      <c r="C131" s="16" t="n"/>
-      <c r="D131" s="16" t="n"/>
-      <c r="E131" s="16" t="n"/>
-      <c r="F131" s="17" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="n"/>
-      <c r="B132" s="7" t="inlineStr">
-        <is>
-          <t>LOT 1 — NOSAČI ZA FOTONAPONSKE PANELE (GROUND SUPPORT)</t>
-        </is>
-      </c>
-      <c r="C132" s="9" t="n"/>
-      <c r="D132" s="9" t="n"/>
-      <c r="E132" s="9" t="n"/>
-      <c r="F132" s="8">
-        <f>'LOT 1'!F50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="9" t="n"/>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>LOT 2 — DIZEL ELEKTRIČNI AGREGAT U POSTOJEĆEM KONTEJNERU</t>
-        </is>
-      </c>
-      <c r="C133" s="9" t="n"/>
-      <c r="D133" s="9" t="n"/>
-      <c r="E133" s="9" t="n"/>
-      <c r="F133" s="8">
-        <f>F129</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="15" t="inlineStr">
-        <is>
-          <t>SVE UKUPNO (LOT 1 + LOT 2) bez PDV-a [KM]:</t>
         </is>
       </c>
       <c r="B134" s="16" t="n"/>
       <c r="C134" s="16" t="n"/>
       <c r="D134" s="16" t="n"/>
       <c r="E134" s="17" t="n"/>
-      <c r="F134" s="10">
-        <f>SUM(F132:F133)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="15" t="inlineStr">
-        <is>
-          <t>Popust [%]:</t>
-        </is>
-      </c>
-      <c r="B135" s="16" t="n"/>
-      <c r="C135" s="16" t="n"/>
-      <c r="D135" s="16" t="n"/>
-      <c r="E135" s="17" t="n"/>
-      <c r="F135" s="10" t="n"/>
-    </row>
+      <c r="F134" s="14">
+        <f>F94+F124+F132</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135"/>
     <row r="136">
-      <c r="A136" s="15" t="inlineStr">
-        <is>
-          <t>SVE UKUPNO sa popustom bez PDV-a [KM]:</t>
+      <c r="A136" s="21" t="inlineStr">
+        <is>
+          <t>REKAPITULACIJA</t>
         </is>
       </c>
       <c r="B136" s="16" t="n"/>
       <c r="C136" s="16" t="n"/>
       <c r="D136" s="16" t="n"/>
-      <c r="E136" s="17" t="n"/>
-      <c r="F136" s="10">
-        <f>F134*(1-IF(F135="",0,F135/100))</f>
-        <v/>
-      </c>
+      <c r="E136" s="16" t="n"/>
+      <c r="F136" s="17" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="15" t="inlineStr">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>LOT 1 — NOSAČI ZA FOTONAPONSKE PANELE (GROUND SUPPORT)</t>
+        </is>
+      </c>
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="8">
+        <f>'LOT 1'!F50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="n"/>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>LOT 2 — DIZEL ELEKTRIČNI AGREGAT U POSTOJEĆEM KONTEJNERU</t>
+        </is>
+      </c>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="9" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="8">
+        <f>F134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="15" t="inlineStr">
+        <is>
+          <t>SVE UKUPNO (LOT 1 + LOT 2) bez PDV-a [KM]:</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="n"/>
+      <c r="C139" s="16" t="n"/>
+      <c r="D139" s="16" t="n"/>
+      <c r="E139" s="17" t="n"/>
+      <c r="F139" s="10">
+        <f>SUM(F137:F138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="15" t="inlineStr">
+        <is>
+          <t>Popust [%]:</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="15" t="inlineStr">
+        <is>
+          <t>SVE UKUPNO sa popustom bez PDV-a [KM]:</t>
+        </is>
+      </c>
+      <c r="F141">
+        <f>F139*(1-IF(F140="",0,F140/100))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="15" t="inlineStr">
         <is>
           <t>Iznos PDV-a (17%) [KM]:</t>
         </is>
       </c>
-      <c r="B137" s="16" t="n"/>
-      <c r="C137" s="16" t="n"/>
-      <c r="D137" s="16" t="n"/>
-      <c r="E137" s="17" t="n"/>
-      <c r="F137" s="10">
-        <f>F136*0.17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="inlineStr">
+      <c r="F142">
+        <f>F141*0.17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="15" t="inlineStr">
         <is>
           <t>SVE UKUPNO sa popustom i PDV-om [KM]:</t>
         </is>
       </c>
-      <c r="B138" s="16" t="n"/>
-      <c r="C138" s="16" t="n"/>
-      <c r="D138" s="16" t="n"/>
-      <c r="E138" s="17" t="n"/>
-      <c r="F138" s="10">
-        <f>F136+F137</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="22" t="inlineStr">
+      <c r="F143">
+        <f>F141+F142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="22" t="inlineStr">
         <is>
           <t>NAPOMENA:</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="18" t="inlineStr">
-        <is>
-          <t>- Nabavka je podijeljena na dva LOT-a. Ponuđač može dostaviti ponudu za JEDAN ili OBA LOT-a. Ugovor se dodjeljuje po LOT-u, prema kriteriju najniže cijene tehnički zadovoljavajuće ponude.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="18" t="inlineStr">
-        <is>
-          <t>- Procijenjena vrijednost nabavke: LOT 1 = 15.000,00 KM, LOT 2 = 35.000,00 KM, UKUPNO 50.000,00 KM bez PDV-a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="18" t="inlineStr">
-        <is>
-          <t>- Ugovorne obaveze nastaju po upućivanju pismenog zahtjeva/narudžbe od strane BH Telecom-a.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="18" t="inlineStr">
-        <is>
-          <t>- Količine u Tačkama 2. i 5. su orijentacione i utvrđene na osnovu podataka iz RFI dokumenta i Projektnog zadatka. Konačne količine utvrđuju se elaboratom montaže i geodetskim snimkom, a obračunavaju se po stvarno izvedenim količinama.</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="18" t="inlineStr">
-        <is>
-          <t>- LOT 2 obuhvata montažu i uvezivanje sistema DO POTPUNE GOTOVOSTI.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>- Orijentaciona potrošnja goriva agregata 22 kVA pri opterećenju od 75 % iznosi cca 3,2 l/h (procjena razmjerna snazi, u odnosu na ranije razmatran model od 18 kVA). Pri projektovanom godišnjem radu do 250 h (standby režim prema ISO 8528) to iznosi cca 800 l godišnje, odnosno spremnik od 500 l obezbjeđuje autonomiju od cca 7–8 mjeseci (cca 0,6 godine) između dopunjavanja. Ponuđač je dužan dostaviti stvarne podatke o potrošnji za ponuđeni tip DEA.</t>
+          <t>- Nabavka je podijeljena na dva LOT-a. Ponuđač može dostaviti ponudu za JEDAN ili OBA LOT-a. Ugovor se dodjeljuje po LOT-u, prema kriteriju najniže cijene tehnički zadovoljavajuće ponude.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="18" t="inlineStr">
         <is>
+          <t>- Procijenjena vrijednost nabavke: LOT 1 = 15.000,00 KM, LOT 2 = 35.000,00 KM, UKUPNO 50.000,00 KM bez PDV-a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
+        <is>
+          <t>- Ugovorne obaveze nastaju po upućivanju pismenog zahtjeva/narudžbe od strane BH Telecom-a.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="18" t="inlineStr">
+        <is>
+          <t>- Količine u Tačkama 2. i 5. su orijentacione i utvrđene na osnovu podataka iz RFI dokumenta i Projektnog zadatka. Konačne količine utvrđuju se elaboratom montaže i geodetskim snimkom, a obračunavaju se po stvarno izvedenim količinama.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="18" t="inlineStr">
+        <is>
+          <t>- LOT 2 obuhvata montažu i uvezivanje sistema DO POTPUNE GOTOVOSTI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="18" t="inlineStr">
+        <is>
+          <t>- Orijentaciona potrošnja goriva agregata 22 kVA pri opterećenju od 75 % iznosi cca 3,2 l/h (procjena razmjerna snazi, u odnosu na ranije razmatran model od 18 kVA). Pri projektovanom godišnjem radu do 250 h (standby režim prema ISO 8528) to iznosi cca 800 l godišnje, odnosno spremnik od 500 l obezbjeđuje autonomiju od cca 7–8 mjeseci (cca 0,6 godine) između dopunjavanja. Ponuđač je dužan dostaviti stvarne podatke o potrošnji za ponuđeni tip DEA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="18" t="inlineStr">
+        <is>
           <t>- Grafički prilozi (situacija postojećeg i budućeg stanja, presjek, dispozicija opreme) dati su u PRILOGU III tenderske dokumentacije.</t>
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="B149" s="1" t="inlineStr">
+    <row r="153"/>
+    <row r="154">
+      <c r="B154" s="1" t="inlineStr">
         <is>
           <t>Datum:  ___________________________</t>
         </is>
       </c>
-      <c r="E149" s="1" t="inlineStr">
+      <c r="E154" s="1" t="inlineStr">
         <is>
           <t>Potpis i pečat Ponuđača:  ___________________________</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="13">
     <mergeCell ref="A138:E138"/>
     <mergeCell ref="A145:F145"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A141:F141"/>
     <mergeCell ref="A144:F144"/>
     <mergeCell ref="A137:E137"/>
-    <mergeCell ref="A131:F131"/>
-    <mergeCell ref="A140:F140"/>
     <mergeCell ref="A147:F147"/>
     <mergeCell ref="A136:E136"/>
     <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A129:E129"/>
-    <mergeCell ref="A143:F143"/>
     <mergeCell ref="A135:E135"/>
-    <mergeCell ref="A142:F142"/>
-    <mergeCell ref="A91:E91"/>
     <mergeCell ref="A134:E134"/>
     <mergeCell ref="A146:F146"/>
     <mergeCell ref="A127:E127"/>

--- a/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
+++ b/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
@@ -1321,7 +1321,7 @@
  - MJERODAVNO OPTEREĆENJE VJETROM: qp ≥ 1,20 kN/m² (udar 3 s ≈ 45 m/s) prema ovjerenoj projektnoj dokumentaciji lokacije i BAS EN 1991-1-4 sa BiH nacionalnim aneksom, uz primjenu faktora orografije za izloženi planinski vrh na 1076 m n.v. Koeficijent sile cf ≥ 1,5 pri 45° prema EN 1991-1-4 §7.3, osim ako se proračunom dokaže drugačije. Površina izloženosti vjetru 10,55 m² po nosaču (2305 × 4576 mm). Projektne sile po nosaču (GSN, γQ=1,5 / γG,fav=0,9): podizanje ≥18,1 kN, horizontalna sila ≥13,4 kN, moment prevrtanja ≥62,8 kNm. Mjerodavni su podizanje (uplift) i prevrtanje, a ne nosivost tla. NAPOMENA: kataloški nosač tipa A ima deklarisanu otpornost 31 m/s (0,52 kN/m²) pri 45° i 40 m/s (0,87 kN/m²) pri 15°/25°, što je ISPOD opterećenja ovog lokaliteta čak i za manje polje; Ponuđač je stoga dužan ponuditi konstrukciju dimenzionisanu i dokazanu za stvarno opterećenje lokaliteta, uz pisanu potvrdu proizvođača za konkretnu lokaciju (planinski vrh) ako se ipak nudi kataloški proizvod
  - materijal i izrada: konstrukcijski čelik S275JR (S355JR za stubove) prema EN 10025-2, šuplji profili prema EN 10219 — stubovi min. RHS 80×80×4, rigle min. RHS 60×40×3, ili bilo koji presjek za koji se proračunom dokaže najmanje jednak otporni moment; antikorozivna zaštita vrućim cinčanjem prema EN ISO 1461 min. 70 µm lokalno / 85 µm srednje (klasa korozivnosti C4); zavarivanje prema EN 1090-2 klasa izvedbe EXC2; CE označavanje i izjava o svojstvima prema EN 1090-1; konstrukcijski vijci M16 klase 8.8 prema EN 15048, pričvrsni pribor modula A2/A4 nehrđajući
  - spojni pribor: nehrđajući čelik A2/A4
- - uključeno ožičenje i povezivanje sva tri polja panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. Tačku 1.6a i crtež E-01): PV-1 i PV-2 paralelno na rutu 1, PV-3 samostalno na rutu 2</t>
+ - uključeno ožičenje i povezivanje panela do PVDB distribucije preko po-string DC odvodnika prenapona (v. Tačku 1.6a i crtež E-01): 12 modula se povezuje u DVA STRINGA po 6 modula (string 1 — nosači PV-1 i PV-2; string 2 — nosači PV-2 i PV-3), po jedan string na svaku od dvije rute PVDB ormara</t>
         </is>
       </c>
       <c r="C12" s="79" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="B34" s="91" t="inlineStr">
         <is>
-          <t>Isporuka i polaganje DC solarnog kabla 1×6 mm² (H1Z2Z2-K) od fotonaponskih panela do PVDB distribucije, uključujući MC4 konektore, obujmice i UV-otporne kanalice. NAPOMENA: završni priključak na ulaznu stezaljku iSSU modula izvesti presjekom 4 mm² prema izričitom zahtjevu proizvođača. Pad napona pri Imp 13,67 A i dužini 25 m iznosi 0,78 %. 3 nosača × 2 × 25,00 m</t>
+          <t>Isporuka i polaganje DC solarnog kabla 1×6 mm² (H1Z2Z2-K) od fotonaponskih panela do PVDB distribucije, uključujući MC4 konektore, obujmice i UV-otporne kanalice. NAPOMENA: završni priključak na ulaznu stezaljku iSSU modula izvesti presjekom 4 mm² prema izričitom zahtjevu proizvođača. Pad napona pri Imp 13,67 A i dužini 25 m iznosi 0,78 %. 2 stringa × 2 × 25,00 m</t>
         </is>
       </c>
       <c r="C34" s="89" t="inlineStr">
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="D34" s="89" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E34" s="41" t="n"/>
       <c r="F34" s="41">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="B36" s="91" t="inlineStr">
         <is>
-          <t>Isporuka i ugradnja odvodnika prenapona DC, tip 2 (Iimp ≥5 kA, Ucpv ≥425 V), za svaki string, sa pripadajućim rastavnim osiguračima, u PVDB ormaru iz Tačke 1.6 ili u zasebnom kućištu min. IP55. Po jedan komplet uz svako od tri polja panela (v. Tačku 1.1) zbog dužine DC trase od 25 m; PV-1 i PV-2 se spajaju paralelno prije PVDB rute 1, PV-3 ide samostalno na rutu 2 (v. crtež E-01).</t>
+          <t>Isporuka i ugradnja odvodnika prenapona DC, tip 2 (Iimp ≥5 kA, Ucpv ≥425 V), ZA SVAKI STRING, sa pripadajućim rastavnim osiguračima, u PVDB ormaru iz Tačke 1.6 ili u zasebnom kućištu min. IP55. Po jedan komplet po stringu (2 stringa × 6 modula, v. Tačku 1.1 i crtež E-01), zbog dužine DC trase od 25 m.</t>
         </is>
       </c>
       <c r="C36" s="89" t="inlineStr">
@@ -1634,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" s="89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" s="41" t="n"/>
       <c r="F36" s="41">
@@ -2889,7 +2889,7 @@
       <c r="A58" s="9" t="n"/>
       <c r="B58" s="61" t="inlineStr">
         <is>
-          <t>Opšte napomene  NOSIVOST PODA KONTEJNERA: mjerodavna projektna vrijednost je 2,00 kN/m² prema Projektnom zadatku. Ranije navedenih 10,00 kN/m² preuzeto je iz statičkog proračuna tipskog kontejnera K3, a na ovoj lokaciji ugrađen je kontejner tipa K2, pa ta vrijednost NIJE mjerodavna. Agregat (385 kg mokro na 0,96 m² = 3,93 kN/m²) i pun spremnik (≈590 kg na 0,63 m² = 9,2 kN/m²) oba prekoračuju projektnu nosivost, zbog čega je OBAVEZAN čelični ram/roštilj za raznošenje opterećenja ispod skida I ispod tankvane, sa prenosom opterećenja na temeljnu konstrukciju, dokazan statičkim proračunom iz Tačke 4.4.Napomena uz Tačku 4: DEA se ugrađuje u postojeći kontejner na lokaciji, u "inside skid" izvedbi (agregat na zajedničkom nosivom skid-okviru, bez vlastitog vanjskog kućišta, jer funkciju kućišta preuzima kontejner). Referentna izvedba data je u Prilogu III</t>
+          <t>Opšte napomene  NOSIVOST PODA KONTEJNERA: podna konstrukcija je dimenzionisana na ukupno opterećenje (g+p) 10,00 kN/m², prema ovjerenom projektu lokacije (SITE-PROJECT-SJEDNICA-Bileca-K2-S38-m, „04 AG dio", tačka 4.4.2.3 PODNA KONSTRUKCIJA; sekundarni nosači 5,10 kN/m', primarni 15,00 kN/m'). Vrijednost 2,00 kN/m² iz istog projekta odnosi se SAMO na pokretno opterećenje prohodnog dijela poda i nije mjerodavna za oslanjanje opreme. Agregat (385 kg mokro na 0,96 m² = 3,93 kN/m²) i pun spremnik (≈590 kg na 0,63 m² = 9,2 kN/m²) ostaju unutar 10,00 kN/m², ali su KONCENTRISANA opterećenja na malom broju sekundarnih nosača, dok je 10,00 kN/m² ravnomjerno raspodijeljeno opterećenje. Zbog toga je OBAVEZAN čelični ram/roštilj za raznošenje opterećenja ispod skida I ispod tankvane, sa prenosom na primarne nosače, dokazan proračunom iz Tačke 4.4.Napomena uz Tačku 4: DEA se ugrađuje u postojeći kontejner na lokaciji, u "inside skid" izvedbi (agregat na zajedničkom nosivom skid-okviru, bez vlastitog vanjskog kućišta, jer funkciju kućišta preuzima kontejner). Referentna izvedba data je u Prilogu III</t>
         </is>
       </c>
       <c r="C58" s="9" t="n"/>
@@ -3149,8 +3149,8 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>OBAVEZAN statički proračun nosivosti podne konstrukcije postojećeg kontejnera, ovjeren od strane ovlaštenog inženjera, te izvođenje OJAČANJA poda. Ojačanje obuhvata izradu i ugradnju čeličnog roštilja/rama za raznošenje opterećenja ISPOD SKIDA AGREGATA I ISPOD TANKVANE SA SPREMNIKOM, sa prenosom opterećenja na temeljnu konstrukciju kontejnera, uključujući antikorozivnu zaštitu i sav spojni materijal.
-OBRAZLOŽENJE: mjerodavna projektna nosivost poda je 2,00 kN/m² prema Projektnom zadatku. Agregat daje 3,93 kN/m² (385 kg mokro na 0,96 m²), a pun spremnik 9,2 kN/m² (≈590 kg na 0,63 m²) — oba prekoračuju projektnu vrijednost, pa je ojačanje NEOPHODNO, a ne uslovno. Ranija formulacija se pozivala na proračun tipskog kontejnera K3 (10,00 kN/m²), koji NIJE mjerodavan jer je na ovoj lokaciji ugrađen kontejner tipa K2.
+          <t>OBAVEZAN statički proračun nosivosti podne konstrukcije postojećeg kontejnera, ovjeren od strane ovlaštenog inženjera, te izrada i ugradnja čeličnog roštilja/rama za RAZNOŠENJE OPTEREĆENJA ispod skida agregata I ispod tankvane sa spremnikom, sa prenosom opterećenja na primarne nosače podne konstrukcije, uključujući antikorozivnu zaštitu i sav spojni materijal.
+OBRAZLOŽENJE: pod je dimenzionisan na 10,00 kN/m² ukupnog RAVNOMJERNO RASPODIJELJENOG opterećenja (ovjereni projekat lokacije, „04 AG dio", tačka 4.4.2.3). Agregat (3,93 kN/m²) i pun spremnik (9,2 kN/m²) su ispod te vrijednosti po površini, ali djeluju koncentrisano na malom broju sekundarnih nosača (HOP 100×50×3 na razmaku 0,51 m), zbog čega se opterećenje mora raznijeti na primarne nosače. Ponuđač proračunom dokazuje raspodjelu i dimenzije rama.
 Zapremina spremnika se ne umanjuje.</t>
         </is>
       </c>

--- a/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
+++ b/bht-sjednica-final-review/TD-OUTPUT/3.1 PRILOG II TD - predmjer Sjednica Bileca.xlsx
@@ -2979,7 +2979,7 @@
       <c r="B64" s="7" t="inlineStr">
         <is>
           <t>Isporuka, montaža i povezivanje dvoplašnog spremnika dizel goriva zapremine 500 l (0,5 m³), izrađenog od čeličnog lima, sa svim spojnim priborom, cjevovodima i armaturama.
- - referentne dimenzije spremnika 1050 × 600 × 1310 mm, masa prazan 170 kg (pun ≈590 kg); smještaj uz SJEVERNI zid kontejnera u tankvani iz Tačke 4.3, prema crtežu M-01</t>
+ - referentne dimenzije spremnika 1050 × 600 × 1310 mm, masa prazan 170 kg (pun ≈590 kg); smještaj uz JUŽNI zid kontejnera u tankvani iz Tačke 4.3, prema crtežu M-01</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3228,7 +3228,7 @@
       <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Isporuka i montaža fiksne žaluzine na kraju kanala za odvod toplog zraka, dimenzija 600 × 600 mm, sa zaštitnom mrežicom, komplet sa montažnim materijalom.
-RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u ZAPADNI zid kontejnera, na osi radijatora agregata. Topli zrak se NE smije izbacivati prema SJEVERNOJ strani, gdje se nalaze postojeći vanjski ormari ICC330-H1 i MTS9302.</t>
+RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u ZAPADNI zid kontejnera, na osi radijatora agregata. Topli zrak i izduv se NE smiju izbacivati prema SJEVERNOJ strani, gdje se nalaze postojeći vanjski ormari ICC330-H1 i MTS9302 i gdje se nalazi usis svježeg zraka.</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -3254,7 +3254,7 @@
       <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Isporuka i montaža vanjske fiksne žaluzine za dovod svježeg zraka, dimenzija 500 × 700 mm, sa zaštitnom mrežicom. Žaluzine postaviti tako da se spriječi ulaz vode u kontejner prilikom padavina.
-RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u JUŽNI zid kontejnera, na istočnom kraju, sa donjom ivicom na cca 0,30 m od poda. Prostorna udaljenost od izduva i od odušne cijevi spremnika ≥3 m. Nije dozvoljeno izvesti dovod zraka kroz ulazna vrata.</t>
+RASPORED (OBAVEZNO, prema crtežu M-01): žaluzina se ugrađuje u SJEVERNI zid kontejnera, na istočnom kraju, sa donjom ivicom na cca 0,30 m od poda. Sjeverna strana je zasjenjena i daje najhladniji usisni zrak, čime se poboljšava hlađenje agregata. Žaluzina se postavlja istočno od vanjskih ormara ICC330-H1/MTS9302 kako se ne bi usisavao topli zrak sa njih. Prostorna udaljenost od izduva i od odušne cijevi spremnika ≥3 m. Nije dozvoljeno izvesti dovod zraka kroz ulazna vrata.</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
